--- a/config/CACHE_GEOCODIFICACION.xlsx
+++ b/config/CACHE_GEOCODIFICACION.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:N299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="N52" s="1" t="n">
-        <v>46233.47480167286</v>
+        <v>46233.47480167824</v>
       </c>
     </row>
     <row r="53">
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="N53" s="1" t="n">
-        <v>46233.47483984689</v>
+        <v>46233.47483984954</v>
       </c>
     </row>
     <row r="54">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="N54" s="1" t="n">
-        <v>46233.47488727898</v>
+        <v>46233.47488728009</v>
       </c>
     </row>
     <row r="55">
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="N55" s="1" t="n">
-        <v>46233.47492961771</v>
+        <v>46233.47492961805</v>
       </c>
     </row>
     <row r="56">
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="N56" s="1" t="n">
-        <v>46233.4749429471</v>
+        <v>46233.47494295139</v>
       </c>
     </row>
     <row r="57">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="N57" s="1" t="n">
-        <v>46233.47496344044</v>
+        <v>46233.4749634375</v>
       </c>
     </row>
     <row r="58">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="N58" s="1" t="n">
-        <v>46233.47498011489</v>
+        <v>46233.47498011574</v>
       </c>
     </row>
     <row r="59">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="N59" s="1" t="n">
-        <v>46233.47500394908</v>
+        <v>46233.47500394676</v>
       </c>
     </row>
     <row r="60">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="N60" s="1" t="n">
-        <v>46233.47501490678</v>
+        <v>46233.47501490741</v>
       </c>
     </row>
     <row r="61">
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="N61" s="1" t="n">
-        <v>46233.47504201551</v>
+        <v>46233.47504201389</v>
       </c>
     </row>
     <row r="62">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="N62" s="1" t="n">
-        <v>46233.47505675716</v>
+        <v>46233.47505675926</v>
       </c>
     </row>
     <row r="63">
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="N63" s="1" t="n">
-        <v>46233.47510388222</v>
+        <v>46233.47510387732</v>
       </c>
     </row>
     <row r="64">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="N64" s="1" t="n">
-        <v>46233.47514554809</v>
+        <v>46233.47514554398</v>
       </c>
     </row>
     <row r="65">
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="N65" s="1" t="n">
-        <v>46233.47515955956</v>
+        <v>46233.47515956018</v>
       </c>
     </row>
     <row r="66">
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="N66" s="1" t="n">
-        <v>46233.4751710525</v>
+        <v>46233.47517105324</v>
       </c>
     </row>
     <row r="67">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="N67" s="1" t="n">
-        <v>46233.47521813692</v>
+        <v>46233.47521813658</v>
       </c>
     </row>
     <row r="68">
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="N68" s="1" t="n">
-        <v>46233.47527287481</v>
+        <v>46233.47527287037</v>
       </c>
     </row>
     <row r="69">
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="N69" s="1" t="n">
-        <v>46233.47529838508</v>
+        <v>46233.47529837963</v>
       </c>
     </row>
     <row r="70">
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="N70" s="1" t="n">
-        <v>46233.4753249299</v>
+        <v>46233.47532493056</v>
       </c>
     </row>
     <row r="71">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="N71" s="1" t="n">
-        <v>46233.47533675843</v>
+        <v>46233.47533675926</v>
       </c>
     </row>
     <row r="72">
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="N72" s="1" t="n">
-        <v>46233.47535162023</v>
+        <v>46233.47535162037</v>
       </c>
     </row>
     <row r="73">
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="N73" s="1" t="n">
-        <v>46233.47540144955</v>
+        <v>46233.47540144676</v>
       </c>
     </row>
     <row r="74">
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="N74" s="1" t="n">
-        <v>46233.47542126953</v>
+        <v>46233.47542127315</v>
       </c>
     </row>
     <row r="75">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="N75" s="1" t="n">
-        <v>46233.47543887299</v>
+        <v>46233.47543887731</v>
       </c>
     </row>
     <row r="76">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N76" s="1" t="n">
-        <v>46233.47545277188</v>
+        <v>46233.4754527662</v>
       </c>
     </row>
     <row r="77">
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="N77" s="1" t="n">
-        <v>46233.47547696838</v>
+        <v>46233.47547696759</v>
       </c>
     </row>
     <row r="78">
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="N78" s="1" t="n">
-        <v>46233.47548586257</v>
+        <v>46233.47548586805</v>
       </c>
     </row>
     <row r="79">
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="N79" s="1" t="n">
-        <v>46233.47551263941</v>
+        <v>46233.47551263889</v>
       </c>
     </row>
     <row r="80">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="N80" s="1" t="n">
-        <v>46233.47556609687</v>
+        <v>46233.47556609954</v>
       </c>
     </row>
     <row r="81">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="N81" s="1" t="n">
-        <v>46233.47560785457</v>
+        <v>46233.4756078588</v>
       </c>
     </row>
     <row r="82">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="N82" s="1" t="n">
-        <v>46233.47565767908</v>
+        <v>46233.47565767361</v>
       </c>
     </row>
     <row r="83">
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="N83" s="1" t="n">
-        <v>46233.47570627606</v>
+        <v>46233.47570627315</v>
       </c>
     </row>
     <row r="84">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="N84" s="1" t="n">
-        <v>46233.47571907059</v>
+        <v>46233.47571907407</v>
       </c>
     </row>
     <row r="85">
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="N85" s="1" t="n">
-        <v>46233.47574179216</v>
+        <v>46233.47574179398</v>
       </c>
     </row>
     <row r="86">
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="N86" s="1" t="n">
-        <v>46233.47575685006</v>
+        <v>46233.47575685185</v>
       </c>
     </row>
     <row r="87">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="N87" s="1" t="n">
-        <v>46233.47577100534</v>
+        <v>46233.47577100695</v>
       </c>
     </row>
     <row r="88">
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="N88" s="1" t="n">
-        <v>46233.47578105854</v>
+        <v>46233.47578105324</v>
       </c>
     </row>
     <row r="89">
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="N89" s="1" t="n">
-        <v>46233.47579576821</v>
+        <v>46233.47579576389</v>
       </c>
     </row>
     <row r="90">
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="N90" s="1" t="n">
-        <v>46233.47580812987</v>
+        <v>46233.475808125</v>
       </c>
     </row>
     <row r="91">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="N91" s="1" t="n">
-        <v>46233.47582920518</v>
+        <v>46233.47582920139</v>
       </c>
     </row>
     <row r="92">
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="N92" s="1" t="n">
-        <v>46233.47586879115</v>
+        <v>46233.4758687963</v>
       </c>
     </row>
     <row r="93">
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="N93" s="1" t="n">
-        <v>46233.47591868293</v>
+        <v>46233.47591868055</v>
       </c>
     </row>
     <row r="94">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="N94" s="1" t="n">
-        <v>46233.47596041564</v>
+        <v>46233.47596041667</v>
       </c>
     </row>
     <row r="95">
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="N95" s="1" t="n">
-        <v>46233.47597943051</v>
+        <v>46233.47597943287</v>
       </c>
     </row>
     <row r="96">
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="N96" s="1" t="n">
-        <v>46233.47598762353</v>
+        <v>46233.47598762732</v>
       </c>
     </row>
     <row r="97">
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="N97" s="1" t="n">
-        <v>46233.47600378688</v>
+        <v>46233.47600378472</v>
       </c>
     </row>
     <row r="98">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="N98" s="1" t="n">
-        <v>46233.4760294291</v>
+        <v>46233.47602943287</v>
       </c>
     </row>
     <row r="99">
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="N99" s="1" t="n">
-        <v>46233.4760794895</v>
+        <v>46233.47607949074</v>
       </c>
     </row>
     <row r="100">
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="N100" s="1" t="n">
-        <v>46233.47609224951</v>
+        <v>46233.47609224537</v>
       </c>
     </row>
     <row r="101">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="N101" s="1" t="n">
-        <v>46233.476104635</v>
+        <v>46233.47610462963</v>
       </c>
     </row>
     <row r="102">
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="N102" s="1" t="n">
-        <v>46233.47611788981</v>
+        <v>46233.47611789352</v>
       </c>
     </row>
     <row r="103">
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="N103" s="1" t="n">
-        <v>46233.47613534501</v>
+        <v>46233.47613534722</v>
       </c>
     </row>
     <row r="104">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="N104" s="1" t="n">
-        <v>46233.47615968764</v>
+        <v>46233.4761596875</v>
       </c>
     </row>
     <row r="105">
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="N105" s="1" t="n">
-        <v>46233.4761687711</v>
+        <v>46233.47616877315</v>
       </c>
     </row>
     <row r="106">
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="N106" s="1" t="n">
-        <v>46233.47618304385</v>
+        <v>46233.47618304398</v>
       </c>
     </row>
     <row r="107">
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="N107" s="1" t="n">
-        <v>46233.47620621412</v>
+        <v>46233.47620621528</v>
       </c>
     </row>
     <row r="108">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="N108" s="1" t="n">
-        <v>46233.47627071216</v>
+        <v>46233.47627071759</v>
       </c>
     </row>
     <row r="109">
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="N109" s="1" t="n">
-        <v>46233.47627835169</v>
+        <v>46233.47627835648</v>
       </c>
     </row>
     <row r="110">
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="N110" s="1" t="n">
-        <v>46233.47630097096</v>
+        <v>46233.47630097222</v>
       </c>
     </row>
     <row r="111">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="N111" s="1" t="n">
-        <v>46233.47632015397</v>
+        <v>46233.47632015046</v>
       </c>
     </row>
     <row r="112">
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="N112" s="1" t="n">
-        <v>46233.4763691738</v>
+        <v>46233.47636917824</v>
       </c>
     </row>
     <row r="113">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="N113" s="1" t="n">
-        <v>46233.47639315262</v>
+        <v>46233.47639314815</v>
       </c>
     </row>
     <row r="114">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="N114" s="1" t="n">
-        <v>46233.47640923804</v>
+        <v>46233.47640923611</v>
       </c>
     </row>
     <row r="115">
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="N115" s="1" t="n">
-        <v>46233.4764528247</v>
+        <v>46233.47645282408</v>
       </c>
     </row>
     <row r="116">
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="N116" s="1" t="n">
-        <v>46233.47650772253</v>
+        <v>46233.4765077199</v>
       </c>
     </row>
     <row r="117">
@@ -6741,7 +6741,7 @@
         </is>
       </c>
       <c r="N117" s="1" t="n">
-        <v>46233.47655129967</v>
+        <v>46233.4765512963</v>
       </c>
     </row>
     <row r="118">
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="N118" s="1" t="n">
-        <v>46233.47657388728</v>
+        <v>46233.47657388889</v>
       </c>
     </row>
     <row r="119">
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="N119" s="1" t="n">
-        <v>46233.47662593982</v>
+        <v>46233.4766259375</v>
       </c>
     </row>
     <row r="120">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="N120" s="1" t="n">
-        <v>46233.47663505092</v>
+        <v>46233.4766350463</v>
       </c>
     </row>
     <row r="121">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="N121" s="1" t="n">
-        <v>46233.47668610713</v>
+        <v>46233.47668611111</v>
       </c>
     </row>
     <row r="122">
@@ -7037,7 +7037,7 @@
         </is>
       </c>
       <c r="N122" s="1" t="n">
-        <v>46233.47673695566</v>
+        <v>46233.47673695602</v>
       </c>
     </row>
     <row r="123">
@@ -7089,7 +7089,7 @@
         </is>
       </c>
       <c r="N123" s="1" t="n">
-        <v>46233.47674785983</v>
+        <v>46233.4767478588</v>
       </c>
     </row>
     <row r="124">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="N124" s="1" t="n">
-        <v>46233.47679917462</v>
+        <v>46233.47679917824</v>
       </c>
     </row>
     <row r="125">
@@ -7205,7 +7205,7 @@
         </is>
       </c>
       <c r="N125" s="1" t="n">
-        <v>46233.47682600235</v>
+        <v>46233.47682600695</v>
       </c>
     </row>
     <row r="126">
@@ -7257,7 +7257,7 @@
         </is>
       </c>
       <c r="N126" s="1" t="n">
-        <v>46233.47683476775</v>
+        <v>46233.47683476852</v>
       </c>
     </row>
     <row r="127">
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="N127" s="1" t="n">
-        <v>46233.47688673883</v>
+        <v>46233.47688673611</v>
       </c>
     </row>
     <row r="128">
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="N128" s="1" t="n">
-        <v>46233.4769261699</v>
+        <v>46233.47692616898</v>
       </c>
     </row>
     <row r="129">
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="N129" s="1" t="n">
-        <v>46233.47693902411</v>
+        <v>46233.47693902778</v>
       </c>
     </row>
     <row r="130">
@@ -7477,7 +7477,7 @@
         </is>
       </c>
       <c r="N130" s="1" t="n">
-        <v>46233.47696295519</v>
+        <v>46233.47696295139</v>
       </c>
     </row>
     <row r="131">
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="N131" s="1" t="n">
-        <v>46233.4770241499</v>
+        <v>46233.47702415509</v>
       </c>
     </row>
     <row r="132">
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="N132" s="1" t="n">
-        <v>46233.47703302523</v>
+        <v>46233.47703302083</v>
       </c>
     </row>
     <row r="133">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="N133" s="1" t="n">
-        <v>46233.47704187078</v>
+        <v>46233.477041875</v>
       </c>
     </row>
     <row r="134">
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="N134" s="1" t="n">
-        <v>46233.47705586653</v>
+        <v>46233.47705586805</v>
       </c>
     </row>
     <row r="135">
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="N135" s="1" t="n">
-        <v>46233.47706544384</v>
+        <v>46233.47706543982</v>
       </c>
     </row>
     <row r="136">
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="N136" s="1" t="n">
-        <v>46233.47711800809</v>
+        <v>46233.47711800926</v>
       </c>
     </row>
     <row r="137">
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="N137" s="1" t="n">
-        <v>46233.47713014448</v>
+        <v>46233.47713013889</v>
       </c>
     </row>
     <row r="138">
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="N138" s="1" t="n">
-        <v>46233.47715923718</v>
+        <v>46233.47715923611</v>
       </c>
     </row>
     <row r="139">
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="N139" s="1" t="n">
-        <v>46233.47716713628</v>
+        <v>46233.4771671412</v>
       </c>
     </row>
     <row r="140">
@@ -8033,7 +8033,7 @@
         </is>
       </c>
       <c r="N140" s="1" t="n">
-        <v>46233.47718349665</v>
+        <v>46233.47718349537</v>
       </c>
     </row>
     <row r="141">
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="N141" s="1" t="n">
-        <v>46233.4772124809</v>
+        <v>46233.47721247685</v>
       </c>
     </row>
     <row r="142">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="N142" s="1" t="n">
-        <v>46233.47722074998</v>
+        <v>46233.47722075231</v>
       </c>
     </row>
     <row r="143">
@@ -8189,7 +8189,7 @@
         </is>
       </c>
       <c r="N143" s="1" t="n">
-        <v>46233.47724426417</v>
+        <v>46233.47724425926</v>
       </c>
     </row>
     <row r="144">
@@ -8241,7 +8241,7 @@
         </is>
       </c>
       <c r="N144" s="1" t="n">
-        <v>46233.47729933923</v>
+        <v>46233.47729934028</v>
       </c>
     </row>
     <row r="145">
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="N145" s="1" t="n">
-        <v>46233.47730651111</v>
+        <v>46233.4773065162</v>
       </c>
     </row>
     <row r="146">
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="N146" s="1" t="n">
-        <v>46233.4773376251</v>
+        <v>46233.47733762732</v>
       </c>
     </row>
     <row r="147">
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="N147" s="1" t="n">
-        <v>46233.47736186098</v>
+        <v>46233.47736186343</v>
       </c>
     </row>
     <row r="148">
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="N148" s="1" t="n">
-        <v>46233.47737475576</v>
+        <v>46233.47737475694</v>
       </c>
     </row>
     <row r="149">
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="N149" s="1" t="n">
-        <v>46233.47738444023</v>
+        <v>46233.47738444444</v>
       </c>
     </row>
     <row r="150">
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="N150" s="1" t="n">
-        <v>46233.47741154976</v>
+        <v>46233.47741155093</v>
       </c>
     </row>
     <row r="151">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="N151" s="1" t="n">
-        <v>46233.4774648915</v>
+        <v>46233.47746489583</v>
       </c>
     </row>
     <row r="152">
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="N152" s="1" t="n">
-        <v>46233.47751746259</v>
+        <v>46233.47751746528</v>
       </c>
     </row>
     <row r="153">
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="N153" s="1" t="n">
-        <v>46233.47755416489</v>
+        <v>46233.47755416667</v>
       </c>
     </row>
     <row r="154">
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="N154" s="1" t="n">
-        <v>46233.47756555928</v>
+        <v>46233.47756555556</v>
       </c>
     </row>
     <row r="155">
@@ -8813,7 +8813,7 @@
         </is>
       </c>
       <c r="N155" s="1" t="n">
-        <v>46233.47757615588</v>
+        <v>46233.47757615741</v>
       </c>
     </row>
     <row r="156">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="N156" s="1" t="n">
-        <v>46233.47760393324</v>
+        <v>46233.47760393519</v>
       </c>
     </row>
     <row r="157">
@@ -8917,7 +8917,7 @@
         </is>
       </c>
       <c r="N157" s="1" t="n">
-        <v>46233.47761583453</v>
+        <v>46233.47761583333</v>
       </c>
     </row>
     <row r="158">
@@ -8969,7 +8969,7 @@
         </is>
       </c>
       <c r="N158" s="1" t="n">
-        <v>46233.47764214287</v>
+        <v>46233.4776421412</v>
       </c>
     </row>
     <row r="159">
@@ -9021,7 +9021,7915 @@
         </is>
       </c>
       <c r="N159" s="1" t="n">
-        <v>46233.47765174966</v>
+        <v>46233.47765174769</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>V3|NOA CASA 23 URB LA FLORESTA DEL CERRO|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>NOA CASA 23 URB. LA FLORESTA DEL CERRO -</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>URBANIZACION. LA FLORESTA DEL CERRO, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>2</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N160" s="1" t="n">
+        <v>46239.48165469897</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>V3|CRA 21 70 6 PIS 2 BARRIO SIN DEFINIR|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>CRA 21 70 6 PIS 2 - BARRIO SIN DEFINIR-.</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>CARRERA 21 # 70-6, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>5.0589339</v>
+      </c>
+      <c r="G161" t="n">
+        <v>-75.4857318</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Carrera 21, La Rambla, Comuna Palogrande, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170002, Colombia</t>
+        </is>
+      </c>
+      <c r="N161" s="1" t="n">
+        <v>46239.48166989585</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>V3|CRA 27 81C 04 CAS 80 RINCON DEL TREBOL|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>CRA 27 81C 04 CAS 80 RINCON DEL TREBOL -</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>CARRERA 27 # 81C-04, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>5.0511889</v>
+      </c>
+      <c r="G162" t="n">
+        <v>-75.4885932</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>2</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Carrera 27, Palermo, Comuna Palogrande, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170004, Colombia</t>
+        </is>
+      </c>
+      <c r="N162" s="1" t="n">
+        <v>46239.48169367753</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>V3|SECTOR PANAMERICANA ANTIGUA BLOQUERA B|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SECTOR PANAMERICANA ANTIGUA BLOQUERA - B</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>REFERENCIA_TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>B, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>5.055734</v>
+      </c>
+      <c r="G163" t="n">
+        <v>-75.491118</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>3</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>B, Avenida Paralela, Guayacanes, Comuna Palogrande, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170004, Colombia</t>
+        </is>
+      </c>
+      <c r="N163" s="1" t="n">
+        <v>46239.48173414249</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>V3|CRA 43A 11A 40 PISO 2 ESTAMBUL|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>CRA 43A 11A 40 PISO 2 - ESTAMBUL</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>CARRERA 43A # 11A-40, ESTAMBUL, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>5.0527281</v>
+      </c>
+      <c r="G164" t="n">
+        <v>-75.52576550000001</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Carrera 43A, Estambul, Comuna La Macarena, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 176001, Colombia</t>
+        </is>
+      </c>
+      <c r="N164" s="1" t="n">
+        <v>46239.48174578161</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>V3|CRA 7 27A 86 AVANZADA|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>CRA 7 27A 86 - AVANZADA</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AVANZADA, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>5.0767431</v>
+      </c>
+      <c r="G165" t="n">
+        <v>-75.51377050000001</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>3</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Avanzada, Comuna San José, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170001, Colombia</t>
+        </is>
+      </c>
+      <c r="N165" s="1" t="n">
+        <v>46239.48178277374</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>V3|CRR 7 27A 85 BARRIO SIN DEFINIR|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>CRR 7 27A 85 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NO_CLASIFICADA</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>CRR 7 27A 85, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N166" s="1" t="n">
+        <v>46239.48179891783</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>V3|CRA 7 27A 96 TACHUELO|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>CRA 7 27A 96 - TACHUELO</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>CARRERA 7, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>5.0759243</v>
+      </c>
+      <c r="G167" t="n">
+        <v>-75.4882856</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>4</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Carrera 7, Solferino, Comuna Nuevo Horizonte, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170002, Colombia</t>
+        </is>
+      </c>
+      <c r="N167" s="1" t="n">
+        <v>46239.48184760204</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>V3|CRA 7 27A 90 TACHUELO|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>CRA 7 27A 90 - TACHUELO</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>CARRERA 7, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>5.0759243</v>
+      </c>
+      <c r="G168" t="n">
+        <v>-75.4882856</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>4</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Carrera 7, Solferino, Comuna Nuevo Horizonte, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170002, Colombia</t>
+        </is>
+      </c>
+      <c r="N168" s="1" t="n">
+        <v>46239.48189117705</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>V3|VDA LA GARRUCHA ZONA RURAL|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>VDA LA GARRUCHA - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>VEREDA LA GARRUCHA, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N169" s="1" t="n">
+        <v>46239.48191160727</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>V3|VDA EL CRUCERO EL PLAN VEREDA EL CRUCE|NEIRA</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>VDA EL CRUCERO EL PLAN - Vereda El Cruce</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Neira</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>VEREDA EL CRUCERO EL PLAN, Neira, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N170" s="1" t="n">
+        <v>46239.48192040396</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>V3|VDA ALTO EL NARANJO FCA EL DIAMANTE VE|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>VDA ALTO EL NARANJO FCA EL DIAMANTE - Ve</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>VEREDA ALTO EL NARANJO FCA EL DIAMANTE, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N171" s="1" t="n">
+        <v>46239.48193257086</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>V3|CRA 5 CLL 10 35 PISO 3 SECTORA LA VARI|NEIRA</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CRA 5 CLL 10 35 PISO 3 - SECTORA LA VARI</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Neira</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>SECTORA LA VARI, Neira, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N172" s="1" t="n">
+        <v>46239.48194792911</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>V3|VDA QUIEBRA DEL BILLAR ZONA RURAL|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>VDA QUIEBRA DEL BILLAR - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>VEREDA QUIEBRA DEL BILLAR, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N173" s="1" t="n">
+        <v>46239.48195795785</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>V3|VDA ALTO BONITO ENSEGUIDA CASA 9 VIA A|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>VDA ALTO BONITO ENSEGUIDA CASA 9 VIA A</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>VEREDA ALTO BONITO ENSEGUIDA CASA 9 VIA A, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N174" s="1" t="n">
+        <v>46239.48198366333</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>V3|VDA SAN JOSE SECTOR CARRILERA VEREDA S|NEIRA</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>VDA SAN JOSE SECTOR CARRILERA - Vereda S</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Neira</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>VEREDA SAN JOSE SECTOR CARRILERA, Neira, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N175" s="1" t="n">
+        <v>46239.48198960529</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>V3|CLL 9 9 33 APT 102 CHIPRE|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>CLL 9 9 33 APT 102 - CHIPRE</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>CALLE 9 # 9-33, CHIPRE, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>5.0738785</v>
+      </c>
+      <c r="G176" t="n">
+        <v>-75.5262348</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Calle 9, Chipre, Comuna Atardeceres, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170001, Colombia</t>
+        </is>
+      </c>
+      <c r="N176" s="1" t="n">
+        <v>46239.4820021603</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>V3|VDA FARALLONES FCA LA NEGRITA|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>VDA FARALLONES FCA LA NEGRITA</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>VEREDA FARALLONES FCA LA NEGRITA, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N177" s="1" t="n">
+        <v>46239.48201223854</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>V3|CLL 50 14 21 EL PROGRESO BARRIO SIN D|LA DORADA</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>CLL 50 #14-21 EL PROGRESO - BARRIO SIN D</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>La Dorada</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>21 EL PROGRESO - BARRIO SIN D SIN D, La Dorada, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N178" s="1" t="n">
+        <v>46239.48202841494</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>V3|CLL 8 8 63 LA MAGDALENA|LA DORADA</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>CLL 8 8 63 - LA MAGDALENA</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>La Dorada</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>CALLE 8 # 8-63, LA MAGDALENA, La Dorada, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>5.4484718</v>
+      </c>
+      <c r="G179" t="n">
+        <v>-74.6623896</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>La Dorada</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Calle 8, La Dorada, Magdalena Caldense, Caldas, RAP del Agua y la Montaña, 175031, Colombia</t>
+        </is>
+      </c>
+      <c r="N179" s="1" t="n">
+        <v>46239.48204016245</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>V3|CLL 10 4 51 LOCAL 1 EL CONEJO|LA DORADA</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>CLL 10 4 51 LOCAL 1 - EL CONEJO</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>La Dorada</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>CALLE 10 # 4-51, La Dorada, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>5.4496126</v>
+      </c>
+      <c r="G180" t="n">
+        <v>-74.66267550000001</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>La Dorada</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>2</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Calle 10, La Dorada, Magdalena Caldense, Caldas, RAP del Agua y la Montaña, 175031, Colombia</t>
+        </is>
+      </c>
+      <c r="N180" s="1" t="n">
+        <v>46239.48206546283</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>V3|PANCOGER ETAPA 2 LOT 569 BARRIO SIN DE|LA DORADA</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>PANCOGER ETAPA 2 LOT 569 - BARRIO SIN DE</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>La Dorada</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>PANCOGER ETAPA 2 - BARRIO SIN DE, La Dorada, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>2</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N181" s="1" t="n">
+        <v>46239.48209553294</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>V3|CRA 6A 40 40 VILLA ANGELICA BARRIO SIN|LA DORADA</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>CRA 6A 40 40 VILLA ANGELICA - BARRIO SIN</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>La Dorada</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>CARRERA 6A # 40-40, La Dorada, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>5.4470965</v>
+      </c>
+      <c r="G182" t="n">
+        <v>-74.66381800000001</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>La Dorada</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>2</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Carrera 6A, La Dorada, Magdalena Caldense, Caldas, RAP del Agua y la Montaña, 253480, Colombia</t>
+        </is>
+      </c>
+      <c r="N182" s="1" t="n">
+        <v>46239.48212239167</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>V3|CDM TABOGA LOT 53 ZONA RURAL|PALESTINA</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>CDM TABOGA LOT 53 - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Palestina</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>CDM TABOGA, Palestina, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>2</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N183" s="1" t="n">
+        <v>46239.48214293867</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>V3|VDA LA PARROQUIA ENTRADA PALESTINA REMOL|PALESTINA</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>VDA LA PARROQUIA ENTRADA PALESTINA REMOL</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Palestina</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>VEREDA LA PARROQUIA ENTRADA PALESTINA REMOL, Palestina, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N184" s="1" t="n">
+        <v>46239.48215812913</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>V3|VEREDA EL TREBOL DESPUES DEL PUESTO DE S|CHINCHINA</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>VEREDA EL TREBOL DESPUES DEL PUESTO DE S</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Chinchina</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>VEREDA EL TREBOL DESPUES DEL PUESTO DE S, Chinchina, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N185" s="1" t="n">
+        <v>46239.48216969222</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>V3|NOA KM 2 AUTOPISTA DEL CAFE CAS 9 ZONA|CHINCHINA</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>NOA KM 2 AUTOPISTA DEL CAFÉ CAS 9 - ZONA</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Chinchina</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>KM 2 AUTOPISTA DEL CAFÉ - ZONA, Chinchina, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>2</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N186" s="1" t="n">
+        <v>46239.48219395501</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>V3|VIA CHINCHINA MANIZALES KM 2 AUTOPISTA D|CHINCHINA</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>VIA CHINCHINA MANIZALES KM 2 AUTOPISTA D</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Chinchina</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NO_CLASIFICADA</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>VIA CHINCHINA MANIZALES KM 2 AUTOPISTA D, Chinchina, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>1</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N187" s="1" t="n">
+        <v>46239.48220413322</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>V3|CRA 17 A 8 17 PIS 1 URB VERDUN II ETP|CHINCHINA</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>CRA 17 A 8 17 PIS 1 URB VERDUN II ETP -</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Chinchina</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>CARRERA 17A # 8-17, Chinchina, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>4.9751826</v>
+      </c>
+      <c r="G188" t="n">
+        <v>-75.61200289999999</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Chinchiná</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>2</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Carrera 17A, Chinchiná, Centrosur, Caldas, RAP del Agua y la Montaña, 176020, Colombia</t>
+        </is>
+      </c>
+      <c r="N188" s="1" t="n">
+        <v>46239.48222903151</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>V3|CRA 17 A 8 17 PIS 2 URB VERDUN II ETP|CHINCHINA</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>CRA 17 A 8 17 PIS 2 URB VERDUN II ETP -</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Chinchina</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>CARRERA 17A # 8-17, Chinchina, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>4.9751826</v>
+      </c>
+      <c r="G189" t="n">
+        <v>-75.61200289999999</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Chinchiná</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>2</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Carrera 17A, Chinchiná, Centrosur, Caldas, RAP del Agua y la Montaña, 176020, Colombia</t>
+        </is>
+      </c>
+      <c r="N189" s="1" t="n">
+        <v>46239.48225143551</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>V3|NOA VEREDA EL BOSQUE ZONA RURAL|MANZANARES</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>NOA VEREDA EL BOSQUE - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Manzanares</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>VEREDA EL BOSQUE, Manzanares, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N190" s="1" t="n">
+        <v>46239.48227272968</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>V3|CLL 6 5 74 PARTE ALTA PISO 3 ZONA CENT|MANZANARES</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>CLL 6 5 74 PARTE ALTA PISO 3 - ZONA CENT</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Manzanares</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>CALLE 6 # 5-74, Manzanares, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>5.2547707</v>
+      </c>
+      <c r="G191" t="n">
+        <v>-75.1551432</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Manzanares</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>2</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Calle 6, Manzanares, Alto Oriente, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N191" s="1" t="n">
+        <v>46239.48229947377</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>V3|BRR SAN VICENTE SAN VICENTE|MARQUETALIA</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>BRR SAN VICENTE - SAN VICENTE</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Marquetalia</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>REFERENCIA_TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>SAN VICENTE, Marquetalia, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>3</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N192" s="1" t="n">
+        <v>46239.48233713442</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>V3|CRA 5A 4B 27 ARRAYANES LOS ARRAYANES|MARQUETALIA</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>CRA 5A 4B 27 ARRAYANES - LOS ARRAYANES</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Marquetalia</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>CARRERA 5A # 4B-27, Marquetalia, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>5.3001749</v>
+      </c>
+      <c r="G193" t="n">
+        <v>-75.05300130000001</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Marquetalia</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>2</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Carrera 5A, Alegrias, Marquetalia, Alto Oriente, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N193" s="1" t="n">
+        <v>46239.48236150593</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>V3|VDA SEBASTOPOL ZONA RURAL|PENSILVANIA</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>VDA SEBASTOPOL - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Pensilvania</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>VEREDA SEBASTOPOL, Pensilvania, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>5.3759505</v>
+      </c>
+      <c r="G194" t="n">
+        <v>-75.0651147</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Pensilvania</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Sebastopol, Pensilvania, Alto Oriente, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N194" s="1" t="n">
+        <v>46239.48237323699</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>V3|CRA 4 5 63 PSO 2 BARRIO SIN DEFINIR|PENSILVANIA</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>CRA 4 5 63 pso 2 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Pensilvania</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>CARRERA 4 # 5-63, Pensilvania, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>5.3837262</v>
+      </c>
+      <c r="G195" t="n">
+        <v>-75.1590884</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Pensilvania</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>1</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Carrera 4, Pensilvania, Alto Oriente, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N195" s="1" t="n">
+        <v>46239.48238930919</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>V3|SEC SAN DANIEL ZONA RURAL|PENSILVANIA</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SEC SAN DANIEL - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Pensilvania</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>REFERENCIA_TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>SECTOR SAN DANIEL, Pensilvania, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L196" t="n">
+        <v>1</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N196" s="1" t="n">
+        <v>46239.48240327382</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>V3|SEC PUEBLO NUEVO LA RAMADA ZONA RURAL|PENSILVANIA</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>SEC PUEBLO NUEVO LA RAMADA - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Pensilvania</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>REFERENCIA_TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>SECTOR PUEBLO NUEVO LA RAMADA, Pensilvania, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N197" s="1" t="n">
+        <v>46239.48241477918</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>V3|VEREDA SAN JOSE LOS NARANJOS ZONA RURA|MANZANARES</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>VEREDA SAN JOSE LOS NARANJOS - ZONA RURA</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Manzanares</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>VEREDA SAN JOSE LOS NARANJOS, Manzanares, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
+        <v>2</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N198" s="1" t="n">
+        <v>46239.48244027089</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>V3|CRA 2 1 130 SEC BARRIO NUEVO ORIENTE PIS|MARQUETALIA</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>CRA 2 1 130 SEC BARRIO NUEVO ORIENTE PIS</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Marquetalia</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>CARRERA 2 # 1-130, Marquetalia, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>5.2967282</v>
+      </c>
+      <c r="G199" t="n">
+        <v>-75.0483783</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Marquetalia</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L199" t="n">
+        <v>2</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Carrera 2, San Gregorio Minitas, Marquetalia, Alto Oriente, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N199" s="1" t="n">
+        <v>46239.4824645835</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>V3|CRA 4 3 25 SAN BERNARDO|PENSILVANIA</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>CRA 4 3 25 - SAN BERNARDO</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Pensilvania</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>CARRERA 4 # 3-25, Pensilvania, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>5.3837262</v>
+      </c>
+      <c r="G200" t="n">
+        <v>-75.1590884</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Pensilvania</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L200" t="n">
+        <v>2</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Carrera 4, Pensilvania, Alto Oriente, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N200" s="1" t="n">
+        <v>46239.48249258479</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>V3|NOA VEREDA PENAGOS FINCA LA MONTANITA|MARQUETALIA</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>NOA VEREDA PENAGOS FINCA LA MONTAÑITA</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Marquetalia</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>VEREDA PENAGOS FINCA LA MONTAÑITA, Marquetalia, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L201" t="n">
+        <v>1</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N201" s="1" t="n">
+        <v>46239.48250156962</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>V3|NOA ALTO BONITO SECTOR LA BALASTRERA V|MARQUETALIA</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>NOA ALTO BONITO SECTOR LA BALASTRERA - V</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Marquetalia</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>REFERENCIA_TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>V, Marquetalia, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>5.2966038</v>
+      </c>
+      <c r="G202" t="n">
+        <v>-75.0546064</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Marquetalia</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L202" t="n">
+        <v>3</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Marquetalia, Alto Oriente, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N202" s="1" t="n">
+        <v>46239.48253939269</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>V3|CLL 8 4 60 PISO 2 APARTAMENTO 203 ZONA|MANZANARES</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>CLL 8 4 60 PISO 2 APARTAMENTO 203 - ZONA</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Manzanares</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>CALLE 8 # 4-60, Manzanares, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>5.2520604</v>
+      </c>
+      <c r="G203" t="n">
+        <v>-75.15626260000001</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Manzanares</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L203" t="n">
+        <v>2</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Calle 8, Manzanares, Alto Oriente, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N203" s="1" t="n">
+        <v>46239.48256953862</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>V3|CLL 8 4 60 PISO 2 APARTAMENTO 204 ZONA|MANZANARES</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>CLL 8 4 60 PISO 2 APARTAMENTO 204 - ZONA</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Manzanares</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>CALLE 8 # 4-60, Manzanares, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>5.2520604</v>
+      </c>
+      <c r="G204" t="n">
+        <v>-75.15626260000001</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Manzanares</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L204" t="n">
+        <v>2</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Calle 8, Manzanares, Alto Oriente, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N204" s="1" t="n">
+        <v>46239.48258645249</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>V3|NOA CRA 2 1 41 EL PORVENIR I|MANZANARES</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>NOA cra 2# 1-41 - EL PORVENIR I</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Manzanares</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>41 - EL PORVENIR I, Manzanares, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L205" t="n">
+        <v>1</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N205" s="1" t="n">
+        <v>46239.4826100978</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>V3|CLL 27 6 06 AVANZADA|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>CLL 27 6 06 - AVANZADA</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>CALLE 27 # 6-06, AVANZADA, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>5.0781156</v>
+      </c>
+      <c r="G206" t="n">
+        <v>-75.5147697</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L206" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Calle 27, Avanzada, Comuna San José, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170001, Colombia</t>
+        </is>
+      </c>
+      <c r="N206" s="1" t="n">
+        <v>46239.48261922898</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>V3|CRA 37 A 65 A 38 B PIO XII PIO XII|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>CRA 37 A 65 A 38 B PIO XII - PIO XII</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>CARRERA 37A # 65A-38, PIO XII B PIO XII, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>5.0491243</v>
+      </c>
+      <c r="G207" t="n">
+        <v>-75.50012649999999</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L207" t="n">
+        <v>1</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Carrera 37A, Pío XII, Comuna Universitaria, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170004, Colombia</t>
+        </is>
+      </c>
+      <c r="N207" s="1" t="n">
+        <v>46239.48263327939</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>V3|SEC BRR SANTA ANA CANCHA DE TIERRA BAR|VILLAMARIA</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>SEC BRR SANTA ANA CANCHA DE TIERRA - BAR</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Villamaria</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>REFERENCIA_TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>BAR, Villamaria, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L208" t="n">
+        <v>3</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N208" s="1" t="n">
+        <v>46239.48266865133</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>V3|SEC BARRIO LOS CHORROS ZONA RURAL|PALESTINA</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SEC BARRIO LOS CHORROS - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Palestina</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>REFERENCIA_TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>SECTOR BARRIO LOS CHORROS, Palestina, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N209" s="1" t="n">
+        <v>46239.48268079428</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>V3|CLL 26A 7 13 INT AVANZADA|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>CLL 26A 7 13 INT - AVANZADA</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>CALLE 26A # 7-13, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>5.0560842</v>
+      </c>
+      <c r="G210" t="n">
+        <v>-75.5150914</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L210" t="n">
+        <v>2</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Calle 26A, Bajo Andes, Comuna La Fuente, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170006, Colombia</t>
+        </is>
+      </c>
+      <c r="N210" s="1" t="n">
+        <v>46239.4827068087</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>V3|VDA LA CABANA SECTOR LOS MANGOS CASA 6 A|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>VDA LA CABAÑA SECTOR LOS MANGOS CASA 6 A</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>VEREDA LA CABAÑA SECTOR LOS MANGOS CASA 6 A, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L211" t="n">
+        <v>1</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N211" s="1" t="n">
+        <v>46239.48272595361</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>V3|CRA 34 SEC FRENTE AL LAVADERO BARRIO S|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>CRA 34 SEC FRENTE AL LAVADERO - BARRIO S</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>BARRIO S S, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N212" s="1" t="n">
+        <v>46239.48273756429</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>V3|CRA 17 23 42 LOC 1 COLON|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>CRA 17 23 42 LOC 1 - COLON</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>CARRERA 17 # 23-42, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>5.0680148</v>
+      </c>
+      <c r="G213" t="n">
+        <v>-75.4953706</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L213" t="n">
+        <v>2</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Carrera 17, La Asunción, Comuna La Estación, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170002, Colombia</t>
+        </is>
+      </c>
+      <c r="N213" s="1" t="n">
+        <v>46239.48276728499</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>V3|CLL 61D 15B 51 2DO PISO PUERTA GRIS|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>CLL 61D 15B 51 - 2DO PISO PUERTA GRIS -</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>CALLE 61D # 15B-51, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>5.0619673</v>
+      </c>
+      <c r="G214" t="n">
+        <v>-75.4821314</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L214" t="n">
+        <v>2</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Calle 61D, Viveros, Comuna Ecoturística Cerro de Oro, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170002, Colombia</t>
+        </is>
+      </c>
+      <c r="N214" s="1" t="n">
+        <v>46239.4827915674</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>V3|CRA 25 69 06 LOC 03 CAMELIA|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CRA 25 69 06 LOC 03 - CAMELIA</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>CARRERA 25 # 69-06, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>5.065234</v>
+      </c>
+      <c r="G215" t="n">
+        <v>-75.5058995</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L215" t="n">
+        <v>2</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Avenida Paralela, Velez, Comuna La Fuente, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170006, Colombia</t>
+        </is>
+      </c>
+      <c r="N215" s="1" t="n">
+        <v>46239.48281721343</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>V3|CLL 55 25 137 ARBOLEDA|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>CLL 55 25 137 - ARBOLEDA</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>CALLE 55 # 25-137, ARBOLEDA, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>5.0601019</v>
+      </c>
+      <c r="G216" t="n">
+        <v>-75.49561989999999</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L216" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Calle 55, Arboleda, Comuna Palogrande, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170004, Colombia</t>
+        </is>
+      </c>
+      <c r="N216" s="1" t="n">
+        <v>46239.48282652591</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>V3|CRA 11B 45F 14 FANNY GONZALEZ|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>CRA 11B 45F 14 - FANNY GONZALEZ</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>CARRERA 11B # 45F-14, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>5.0731577</v>
+      </c>
+      <c r="G217" t="n">
+        <v>-75.4991716</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>2</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Carrera 11B, Peralonso, Comuna Ciudadela del Norte, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170006, Colombia</t>
+        </is>
+      </c>
+      <c r="N217" s="1" t="n">
+        <v>46239.48285541496</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>V3|CLL 118 SEC X ALMAGAS MALTERIA MALTERI|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>CLL 118 SEC X ALMAGAS MALTERIA - MALTERI</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>MALTERI X ALMAGAS MALTERIA - MALTERI, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L218" t="n">
+        <v>1</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N218" s="1" t="n">
+        <v>46239.48288204434</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>V3|CLL 51E 34B 32 PIS 2 SANTOS|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>CLL 51E 34B 32 PIS 2 - SANTOS</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>CALLE 51E # 34B-32, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>5.0706465</v>
+      </c>
+      <c r="G219" t="n">
+        <v>-75.4916453</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
+        <v>2</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Calle 51E, Villahermosa, Comuna Nuevo Horizonte, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170002, Colombia</t>
+        </is>
+      </c>
+      <c r="N219" s="1" t="n">
+        <v>46239.48290248924</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>V3|CALLE 22 NO 20 58 EDIFICIO BANCO GANAD|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>CALLE 22 No 20-58 - EDIFICIO BANCO GANAD</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>58 - EDIFICIO BANCO GANAD, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L220" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N220" s="1" t="n">
+        <v>46239.48291408417</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>V3|CRA 3 G 48 F 52 PIS 2 BOSQUES DEL NORT|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>CRA 3 G 48 F 52 PIS 2 - BOSQUES DEL NORT</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>CARRERA 3G, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>5.0822965</v>
+      </c>
+      <c r="G221" t="n">
+        <v>-75.4892193</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
+        <v>4</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Carrera 3G, Bosques del Norte, Comuna Ciudadela del Norte, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170002, Colombia</t>
+        </is>
+      </c>
+      <c r="N221" s="1" t="n">
+        <v>46239.48296847632</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>V3|CRA 6 C 51 0 9 PIS 2 SOLFERINO|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>CRA 6 C 51 0 9 PIS 2 - SOLFERINO</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>CARRERA 6C # 51-0, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>5.076116</v>
+      </c>
+      <c r="G222" t="n">
+        <v>-75.4872898</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>2</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>Carrera 6C, Solferino, Comuna Nuevo Horizonte, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170002, Colombia</t>
+        </is>
+      </c>
+      <c r="N222" s="1" t="n">
+        <v>46239.48299363743</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>V3|CRA 1 D 48 F 131 SAN SEBASTIAN|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>CRA 1 D 48 F 131 - SAN SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>SAN SEBASTIAN, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>5.0873787</v>
+      </c>
+      <c r="G223" t="n">
+        <v>-75.4880678</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
+        <v>3</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>San Sebastián, Comuna Ciudadela del Norte, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170002, Colombia</t>
+        </is>
+      </c>
+      <c r="N223" s="1" t="n">
+        <v>46239.48302958168</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>V3|NOA VEREDA CRSITALES FLORENCIA|SAMANA</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>NOA VEREDA CRSITALES - FLORENCIA</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Samana</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>VEREDA CRSITALES, Samana, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L224" t="n">
+        <v>2</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N224" s="1" t="n">
+        <v>46239.48305736677</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>V3|SEC SAN DIEGO SAN DIEGO|SAMANA</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>SEC SAN DIEGO - SAN DIEGO</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Samana</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>REFERENCIA_TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>SAN DIEGO, Samana, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>5.6656835</v>
+      </c>
+      <c r="G225" t="n">
+        <v>-74.93366930000001</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Samaná</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L225" t="n">
+        <v>3</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>San Diego, Samaná, Magdalena Caldense, Caldas, RAP Eje Cafetero, Colombia</t>
+        </is>
+      </c>
+      <c r="N225" s="1" t="n">
+        <v>46239.48309719648</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>V3|NUEVO AMANCER APT 1 FLORENCIA|SAMANA</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>NUEVO AMANCER APT 1 - FLORENCIA</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Samana</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NO_CLASIFICADA</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>NUEVO AMANCER APARTAMENTO 1 - FLORENCIA, Samana, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L226" t="n">
+        <v>1</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N226" s="1" t="n">
+        <v>46239.48310557099</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>V3|NUEVO AMANCER APT 2 FLORENCIA|SAMANA</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>NUEVO AMANCER APT 2 - FLORENCIA</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Samana</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>NO_CLASIFICADA</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>NUEVO AMANCER APARTAMENTO 2 - FLORENCIA, Samana, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L227" t="n">
+        <v>1</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N227" s="1" t="n">
+        <v>46239.48311885068</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>V3|VDA JAPON LTE 7 PARCELA 8 ZONA RURAL|LA DORADA</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>VDA JAPON LTE 7 PARCELA 8 - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>La Dorada</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>VEREDA JAPON LOTE 7 PARCELA 8, La Dorada, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L228" t="n">
+        <v>1</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N228" s="1" t="n">
+        <v>46239.48317831155</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>V3|CLL 9 8 9 PLAZA DE FERIAS PISO 1 BARRI|SAMANA</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>CLL 9 8 9 PLAZA DE FERIAS PISO 1 - BARRI</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Samana</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>CALLE 9 # 8-9, Samana, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>5.6666516</v>
+      </c>
+      <c r="G229" t="n">
+        <v>-74.9337032</v>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Samaná</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L229" t="n">
+        <v>2</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Calle 9, Pueblo Nuevo, San Diego, Samaná, Magdalena Caldense, Caldas, RAP Eje Cafetero, Colombia</t>
+        </is>
+      </c>
+      <c r="N229" s="1" t="n">
+        <v>46239.48319979798</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>V3|VDA FIERRITOS VDA FIERRITOS|VICTORIA</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>VDA FIERRITOS - VDA FIERRITOS</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>VEREDA FIERRITOS, Victoria, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L230" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N230" s="1" t="n">
+        <v>46239.48320906563</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>V3|VIA COMFAMILIAR VDA DONA JUANA BARRIO|LA DORADA</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>VIA COMFAMILIAR VDA DOÑA JUANA - BARRIO</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>La Dorada</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>BARRIO, La Dorada, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L231" t="n">
+        <v>3</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N231" s="1" t="n">
+        <v>46239.48324976184</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>V3|VDA COSTA RICA ALTA VEREDA COSTA RICA|SAMANA</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>VDA COSTA RICA ALTA - Vereda Costa Rica</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Samana</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>VEREDA COSTA RICA ALTA, Samana, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>5.3996817</v>
+      </c>
+      <c r="G232" t="n">
+        <v>-74.956737</v>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Samaná</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L232" t="n">
+        <v>1</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>Costa Rica Alta, Samaná, Magdalena Caldense, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N232" s="1" t="n">
+        <v>46239.48325763048</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>V3|CLL 7 7 33 LOCAL BARRIO SIN DEFINIR|SAMANA</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>CLL 7 7 33 LOCAL - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Samana</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>CALLE 7 # 7-33, Samana, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>5.4133524</v>
+      </c>
+      <c r="G233" t="n">
+        <v>-74.9899724</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Samaná</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L233" t="n">
+        <v>2</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>Calle 7, Los Andes, Samaná, Magdalena Caldense, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N233" s="1" t="n">
+        <v>46239.4832880792</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>V3|VDA EL SILENCIO VEREDA EL SILENCIO|SAMANA</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>VDA EL SILENCIO - Vereda El Silencio</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Samana</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>VEREDA EL SILENCIO, Samana, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L234" t="n">
+        <v>1</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N234" s="1" t="n">
+        <v>46239.48330066075</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>V3|VDA LA FE CASERIO ZONA RURAL|VICTORIA</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>VDA LA FE CASERIO - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>VEREDA LA FE CASERIO, Victoria, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L235" t="n">
+        <v>1</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N235" s="1" t="n">
+        <v>46239.48331094409</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>V3|VDA JARDINES 8 ZONA RURAL|SAMANA</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>VDA JARDINES 8 - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Samana</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>VEREDA JARDINES 8, Samana, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L236" t="n">
+        <v>1</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N236" s="1" t="n">
+        <v>46239.48332326627</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>V3|VDA PEQUIN FCA LA TORRE CASA 2|SAMANA</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>VDA PEQUIN FCA LA TORRE CASA 2</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Samana</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>VEREDA PEQUIN FCA LA TORRE CASA 2, Samana, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L237" t="n">
+        <v>1</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N237" s="1" t="n">
+        <v>46239.48333999793</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>V3|CLL 12 A 3 121 PIS 3 BUENOS AIRES|VICTORIA</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>CLL 12 A 3 121 PIS 3 - BUENOS AIRES</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>CALLE 12A # 3-121, Victoria, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>5.3150255</v>
+      </c>
+      <c r="G238" t="n">
+        <v>-74.91040340000001</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L238" t="n">
+        <v>2</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>Calle 12A, Victoria, Magdalena Caldense, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N238" s="1" t="n">
+        <v>46239.48337012407</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>V3|VEREDA FIERRITOS VDA FIERRITOS|VICTORIA</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>VEREDA FIERRITOS - VDA FIERRITOS</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>VEREDA FIERRITOS, Victoria, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L239" t="n">
+        <v>1</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N239" s="1" t="n">
+        <v>46239.48337873552</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>V3|VDA CIMITARRA FINCA NOGALES VDA CIMITA|VICTORIA</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>VDA CIMITARRA FINCA NOGALES - VDA CIMITA</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>VEREDA CIMITARRA FINCA NOGALES, Victoria, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L240" t="n">
+        <v>1</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N240" s="1" t="n">
+        <v>46239.48339511028</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>V3|CLL 25 26 31 PISO 3 SAN JOAQUIN|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>CLL 25 26 31 PISO 3 - SAN JOAQUIN</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>CALLE 25 # 26-31, SAN JOAQUIN, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>5.0678451</v>
+      </c>
+      <c r="G241" t="n">
+        <v>-75.5157071</v>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L241" t="n">
+        <v>1</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>Calle 25, San Joaquín, Comuna Cumanday, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170001, Colombia</t>
+        </is>
+      </c>
+      <c r="N241" s="1" t="n">
+        <v>46239.48341304583</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>V3|CLL 25 26 31 PISO 2 SAN JOAQUIN|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>CLL 25 26 31 PISO 2 - SAN JOAQUIN</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>CALLE 25 # 26-31, SAN JOAQUIN, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>5.0678451</v>
+      </c>
+      <c r="G242" t="n">
+        <v>-75.5157071</v>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L242" t="n">
+        <v>1</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Calle 25, San Joaquín, Comuna Cumanday, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170001, Colombia</t>
+        </is>
+      </c>
+      <c r="N242" s="1" t="n">
+        <v>46239.48341702516</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>V3|CLL 25 26 31 PISO 1 SAN JOAQUIN|MANIZALES</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>CLL 25 26 31 PISO 1 - SAN JOAQUIN</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>CALLE 25 # 26-31, SAN JOAQUIN, Manizales, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>5.0678451</v>
+      </c>
+      <c r="G243" t="n">
+        <v>-75.5157071</v>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Perímetro Urbano Manizales</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L243" t="n">
+        <v>1</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>Calle 25, San Joaquín, Comuna Cumanday, Perímetro Urbano Manizales, Manizales, Centrosur, Caldas, RAP del Agua y la Montaña, 170001, Colombia</t>
+        </is>
+      </c>
+      <c r="N243" s="1" t="n">
+        <v>46239.48342973758</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>V3|VDA EL GALLINAZO LTE 3 ZONA RURAL|VILLAMARIA</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>VDA EL GALLINAZO LTE 3 - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Villamaria</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>VEREDA EL GALLINAZO LOTE 3, Villamaria, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L244" t="n">
+        <v>1</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N244" s="1" t="n">
+        <v>46239.48345014031</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>V3|CLL 10 7 77 PIS 2 BARRIO SIN DEFINIR|VILLAMARIA</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>CLL 10 7 77 PIS 2 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Villamaria</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>CALLE 10 # 7-77, Villamaria, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>5.0449126</v>
+      </c>
+      <c r="G245" t="n">
+        <v>-75.51148980000001</v>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Cabecera Municipal Villamaría</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L245" t="n">
+        <v>1</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>Calle 10, Urapanes, Cabecera Municipal Villamaría, Villamaría, Centrosur, Caldas, RAP del Agua y la Montaña, 176001, Colombia</t>
+        </is>
+      </c>
+      <c r="N245" s="1" t="n">
+        <v>46239.48345894896</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>V3|CLL 5 22 1 PIS 1 BARRIO SIN DEFINIR|VILLAMARIA</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>CLL 5 22 1 PIS 1 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Villamaria</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>CALLE 5 # 22-1, Villamaria, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>5.046274</v>
+      </c>
+      <c r="G246" t="n">
+        <v>-75.5157576</v>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Cabecera Municipal Villamaría</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L246" t="n">
+        <v>1</v>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>Calle 5, La Pradera, Cabecera Municipal Villamaría, Villamaría, Centrosur, Caldas, RAP del Agua y la Montaña, 176001, Colombia</t>
+        </is>
+      </c>
+      <c r="N246" s="1" t="n">
+        <v>46239.48347429789</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>V3|CLL 9 11 65 APTO 2 BARRIO SIN DEFINIR|VILLAMARIA</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>CLL 9 11 65 APTO 2 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Villamaria</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>CALLE 9 # 11-65, Villamaria, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>5.045037</v>
+      </c>
+      <c r="G247" t="n">
+        <v>-75.5125046</v>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Cabecera Municipal Villamaría</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L247" t="n">
+        <v>1</v>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>Calle 9, Urapanes, Cabecera Municipal Villamaría, Villamaría, Centrosur, Caldas, RAP del Agua y la Montaña, 176001, Colombia</t>
+        </is>
+      </c>
+      <c r="N247" s="1" t="n">
+        <v>46239.48348644393</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>V3|URB CAMINO VERDE LOT 21 BARRIO SIN DEF|VILLAMARIA</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>URB CAMINO VERDE LOT 21 - BARRIO SIN DEF</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Villamaria</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>URBANIZACION CAMINO VERDE - BARRIO SIN DEF, Villamaria, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L248" t="n">
+        <v>2</v>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N248" s="1" t="n">
+        <v>46239.48351151699</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>V3|CRA 19 6 A 24 PIS 3 BARRIO SIN DEFINIR|VILLAMARIA</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>CRA 19 6 A 24 PIS 3 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Villamaria</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>CARRERA 19 # 6A-24, Villamaria, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>5.0447102</v>
+      </c>
+      <c r="G249" t="n">
+        <v>-75.5228255</v>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Cabecera Municipal Villamaría</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L249" t="n">
+        <v>1</v>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>Carrera 19, La Pradera, Cabecera Municipal Villamaría, Villamaría, Centrosur, Caldas, RAP del Agua y la Montaña, 176001, Colombia</t>
+        </is>
+      </c>
+      <c r="N249" s="1" t="n">
+        <v>46239.48352452292</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>V3|VDA LA ARGENTINA FRENTE MIRADOR DE LAS O|DOSQUEBRADAS</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>VDA LA ARGENTINA FRENTE MIRADOR DE LAS O</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Dosquebradas</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>VEREDA LA ARGENTINA FRENTE MIRADOR DE LAS O, Dosquebradas, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L250" t="n">
+        <v>1</v>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N250" s="1" t="n">
+        <v>46239.48354262624</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>V3|VDA EL COFRE FIN EL ARENILLO|DOSQUEBRADAS</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>VDA EL COFRE FIN EL ARENILLO</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Dosquebradas</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>VEREDA EL COFRE FIN EL ARENILLO, Dosquebradas, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L251" t="n">
+        <v>1</v>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N251" s="1" t="n">
+        <v>46239.48355219862</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>V3|VDA TRNCAL DE OCCIDENTE CRA 2N 10 142 ME|DOSQUEBRADAS</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>VDA TRNCAL DE OCCIDENTE CRA 2N 10 142 ME</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Dosquebradas</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>VEREDA TRNCAL DE OCCIDENTE CARRERA 2N 10 142 ME, Dosquebradas, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L252" t="n">
+        <v>1</v>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N252" s="1" t="n">
+        <v>46239.48356189461</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>V3|VDA AGUAZUL FCA LA MARIELA ZONA RURAL|DOSQUEBRADAS</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>VDA AGUAZUL FCA LA MARIELA - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Dosquebradas</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>VEREDA AGUAZUL FCA LA MARIELA, Dosquebradas, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L253" t="n">
+        <v>1</v>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N253" s="1" t="n">
+        <v>46239.48357212525</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>V3|VDA BOQUERON LTE 2 2 FCA EL ARROYO EL RE|DOSQUEBRADAS</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>VDA BOQUERON LTE 2 2 FCA EL ARROYO EL RE</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Dosquebradas</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>VEREDA BOQUERON LOTE 2 2 FCA EL ARROYO EL RE, Dosquebradas, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L254" t="n">
+        <v>1</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N254" s="1" t="n">
+        <v>46239.48359250531</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>V3|VDA LA ESPERANZA LTE 12 HUNGRIA PARAJE L|DOSQUEBRADAS</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>VDA LA ESPERANZA LTE 12 HUNGRIA PARAJE L</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Dosquebradas</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>VEREDA LA ESPERANZA LOTE 12 HUNGRIA PARAJE L, Dosquebradas, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L255" t="n">
+        <v>1</v>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N255" s="1" t="n">
+        <v>46239.48360398997</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>V3|CRA 14 23 41 BARRIO SIN DEFINIR|SANTA ROSA DE CABAL</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>CRA 14 23 41 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Cabal</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>CARRERA 14, Santa Rosa de Cabal, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L256" t="n">
+        <v>2</v>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N256" s="1" t="n">
+        <v>46239.48362818224</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>V3|VEREDA LA CIENAGA FINCA EL GUIMO VERED|QUINCHIA</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>VEREDA LA CIENAGA FINCA EL GUIMO - Vered</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Quinchia</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>VEREDA LA CIENAGA FINCA EL GUIMO, Quinchia, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L257" t="n">
+        <v>1</v>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N257" s="1" t="n">
+        <v>46239.48365024781</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>V3|VEREDA SAN JOSE TABACAL VEREDA SAN JOS|QUINCHIA</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>VEREDA SAN JOSE TABACAL - Vereda San Jos</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Quinchia</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>VEREDA SAN JOSE TABACAL, Quinchia, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L258" t="n">
+        <v>1</v>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N258" s="1" t="n">
+        <v>46239.48365392001</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>V3|NOA VEREDA PENA LISA BARRIO SIN DEFINI|QUINCHIA</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>NOA VEREDA PEÑA LISA - BARRIO SIN DEFINI</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Quinchia</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>BARRIO SIN DEFINI, Quinchia, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L259" t="n">
+        <v>3</v>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N259" s="1" t="n">
+        <v>46239.48369132719</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>V3|NOA VEREDA ENCENILLAL VEREDA ENCENILLA|QUINCHIA</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>NOA VEREDA ENCENILLAL - Vereda Encenilla</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Quinchia</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>VEREDA ENCENILLAL, Quinchia, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L260" t="n">
+        <v>1</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N260" s="1" t="n">
+        <v>46239.48370380767</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>V3|VDA GUAYABITO ZONA RURAL|MARMATO</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>VDA GUAYABITO - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Marmato</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>VEREDA GUAYABITO, Marmato, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L261" t="n">
+        <v>1</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N261" s="1" t="n">
+        <v>46239.48371673031</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>V3|NOA GUEYABITO POR LA VIRGEN ZONA RURAL|MARMATO</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>NOA GUEYABITO POR LA VIRGEN - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Marmato</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>NO_CLASIFICADA</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>GUEYABITO POR LA VIRGEN, Marmato, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L262" t="n">
+        <v>1</v>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N262" s="1" t="n">
+        <v>46239.48373270944</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>V3|CRA 5 9 10 BARRIO SIN DEFINIR|BELALCAZAR</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>CRA 5 9 10 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Belalcazar</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>CARRERA 5 # 9-10, Belalcazar, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>4.9928915</v>
+      </c>
+      <c r="G263" t="n">
+        <v>-75.81328550000001</v>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Belalcázar</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L263" t="n">
+        <v>1</v>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>Carrera 5, Belalcázar, Bajo Occidente, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N263" s="1" t="n">
+        <v>46239.48374840063</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>V3|SEC SAN ISIDRO BELALCAZAR|BELALCAZAR</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>SEC SAN ISIDRO BELALCAZAR</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Belalcazar</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>REFERENCIA_TERRITORIAL</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>SECTOR SAN ISIDRO BELALCAZAR, Belalcazar, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L264" t="n">
+        <v>1</v>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N264" s="1" t="n">
+        <v>46239.48375578291</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>V3|VDA LA PALOMA FINCA PORVENIR VEREDA LA|BELALCAZAR</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>VDA LA PALOMA FINCA PORVENIR - Vereda La</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Belalcazar</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>VEREDA LA PALOMA FINCA PORVENIR, Belalcazar, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L265" t="n">
+        <v>1</v>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N265" s="1" t="n">
+        <v>46239.4837681814</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>V3|CRR 2 3 48 APT 1 BARRIO SIN DEFINIR|BELALCAZAR</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>CRR 2 3 48 APT 1 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Belalcazar</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>NO_CLASIFICADA</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>CRR 2 3 48 APARTAMENTO 1, Belalcazar, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L266" t="n">
+        <v>1</v>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N266" s="1" t="n">
+        <v>46239.48378144455</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>V3|CRA 2 3 48 PIS 2 BARRIO SIN DEFINIR|BELALCAZAR</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>CRA 2 3 48 PIS 2 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Belalcazar</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>CARRERA 2 # 3-48, Belalcazar, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>4.9915529</v>
+      </c>
+      <c r="G267" t="n">
+        <v>-75.81226270000001</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Belalcázar</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L267" t="n">
+        <v>1</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>Carrera 2, Belalcázar, Bajo Occidente, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N267" s="1" t="n">
+        <v>46239.48379802345</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>V3|VDA EL MADRONO FINCA ENTRE NUBES VERED|BELALCAZAR</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>VDA EL MADROÑO FINCA ENTRE NUBES - Vered</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Belalcazar</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>VEREDA EL MADROÑO FINCA ENTRE NUBES, Belalcazar, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L268" t="n">
+        <v>1</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N268" s="1" t="n">
+        <v>46239.48381001141</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>V3|VDA LA ROMELIA ZONA RURAL|BELALCAZAR</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>VDA LA ROMELIA - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Belalcazar</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>VEREDA LA ROMELIA, Belalcazar, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L269" t="n">
+        <v>1</v>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N269" s="1" t="n">
+        <v>46239.48382362559</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>V3|URB EL CONTENTO VEREDA EL CONTENTO|SAN JOSE</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>URB EL CONTENTO - Vereda El Contento</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>San Jose</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>VEREDA EL CONTENTO, San Jose, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L270" t="n">
+        <v>3</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N270" s="1" t="n">
+        <v>46239.48386179038</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>V3|CRR 6 18A 16 BARRIO SIN DEFINIR|RIOSUCIO</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>CRR 6 18A 16 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Riosucio</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NO_CLASIFICADA</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>CRR 6 18A 16, Riosucio, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L271" t="n">
+        <v>1</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N271" s="1" t="n">
+        <v>46239.48387331095</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>V3|VDA LA PLAYA PIS 2 VEREDA LA PLAYA|SUPIA</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>VDA LA PLAYA PIS 2 - Vereda La Playa</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Supia</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>VEREDA LA PLAYA PISO 2, Supia, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L272" t="n">
+        <v>1</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N272" s="1" t="n">
+        <v>46239.48389663122</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>V3|VDA SPIRRA SEC POLIDEPORTIVO ZONA RURA|RIOSUCIO</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>VDA SPIRRA SEC POLIDEPORTIVO - ZONA RURA</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Riosucio</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>VEREDA SPIRRA SECTOR POLIDEPORTIVO, Riosucio, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L273" t="n">
+        <v>2</v>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N273" s="1" t="n">
+        <v>46239.48391542218</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>V3|CRA 13 11 59 BARRIO SIN DEFINIR|SANTA ROSA DE CABAL</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>CRA 13 11 59 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Cabal</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>CARRERA 13, Santa Rosa de Cabal, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L274" t="n">
+        <v>2</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N274" s="1" t="n">
+        <v>46239.48394380231</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>V3|CRA 8 B 34 A 18 APT 201 MANANTIAL II|SANTA ROSA DE CABAL</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>CRA 8 B 34 A 18 APT 201 - MANANTIAL II</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Cabal</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>CARRERA 8B, Santa Rosa de Cabal, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L275" t="n">
+        <v>4</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N275" s="1" t="n">
+        <v>46239.48399685419</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>V3|CLL 12 10 34 LOC 1 CENTRO|SANTA ROSA DE CABAL</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>CLL 12 10 34 LOC 1 - CENTRO</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Cabal</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>CALLE 12, Santa Rosa de Cabal, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>San Andrés</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>RECHAZADA</t>
+        </is>
+      </c>
+      <c r="L276" t="n">
+        <v>4</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N276" s="1" t="n">
+        <v>46239.48405244233</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>V3|CRA 14 CLL 12 ESQ|SANTA ROSA DE CABAL</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>CRA 14 CLL 12 ESQ</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Cabal</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>NO GEOCODIFICABLE</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>NO APLICA</t>
+        </is>
+      </c>
+      <c r="L277" t="n">
+        <v>0</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>No fue posible construir una consulta geográfica suficientemente específica.</t>
+        </is>
+      </c>
+      <c r="N277" s="1" t="n">
+        <v>46239.48405247332</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>V3|VDA LA CAMPANA SEC LA POLA ZONA RURAL|NEIRA</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>VDA LA CAMPANA SEC LA POLA - ZONA RURAL-</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Neira</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>VEREDA LA CAMPANA SECTOR LA POLA, Neira, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L278" t="n">
+        <v>1</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N278" s="1" t="n">
+        <v>46239.48406224082</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>V3|VDA LA ESPERANZA FRENTE A LA GAVIOTA Z|RISARALDA</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>VDA LA ESPERANZA FRENTE A LA GAVIOTA - Z</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>VEREDA LA ESPERANZA FRENTE A LA GAVIOTA, Risaralda, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L279" t="n">
+        <v>1</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N279" s="1" t="n">
+        <v>46239.4840779272</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>V3|VDA BETANIA ZONA RURAL|ANSERMA</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>VDA BETANIA - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Anserma</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>VEREDA BETANIA, Anserma, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L280" t="n">
+        <v>1</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N280" s="1" t="n">
+        <v>46239.4840872266</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>V3|LOT 13 CDM CAMPESTRE VALLES DE LA CRUZ|ANSERMA</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>LOT 13 CDM CAMPESTRE VALLES DE LA CRUZ -</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Anserma</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>CDM CAMPESTRE VALLES DE LA CRUZ, Anserma, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L281" t="n">
+        <v>2</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N281" s="1" t="n">
+        <v>46239.48411482705</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>V3|VDA EL PENCIL ZONA RURAL|ANSERMA</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>VDA EL PENCIL - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Anserma</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>VEREDA EL PENCIL, Anserma, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L282" t="n">
+        <v>1</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N282" s="1" t="n">
+        <v>46239.48412764461</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>V3|VDA PATIO BONITO FCA PATIO BONITO ZONA|ANSERMA</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>VDA PATIO BONITO FCA PATIO BONITO - ZONA</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Anserma</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>VEREDA PATIO BONITO FCA PATIO BONITO, Anserma, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L283" t="n">
+        <v>2</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N283" s="1" t="n">
+        <v>46239.48415101103</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>V3|FCA LA TOLDA VEREDA PISAMAL|AGUADAS</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>FCA LA TOLDA - Vereda Pisamal</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Aguadas</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>VEREDA PISAMAL, Aguadas, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L284" t="n">
+        <v>2</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N284" s="1" t="n">
+        <v>46239.48417350868</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>V3|CLL 6 8 23 SAN ANTONIO ARMA ZONA RURAL|AGUADAS</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>CLL 6 8 23 SAN ANTONIO ARMA - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Aguadas</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>CALLE 6 # 8-23, Aguadas, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>5.6125682</v>
+      </c>
+      <c r="G285" t="n">
+        <v>-75.4589079</v>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Aguadas</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L285" t="n">
+        <v>2</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Calle 6, Pore, Aguadas, Norte, Caldas, RAP Eje Cafetero, Colombia</t>
+        </is>
+      </c>
+      <c r="N285" s="1" t="n">
+        <v>46239.48420283484</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>V3|VDA LA UNION VEREDA LA UNION|SALAMINA</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>VDA LA UNIÓN - Vereda La Union</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Salamina</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>VEREDA LA UNIÓN, Salamina, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>5.3372881</v>
+      </c>
+      <c r="G286" t="n">
+        <v>-75.478167</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Salamina</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L286" t="n">
+        <v>1</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>La Aurora, La Unión, Salamina, Norte, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N286" s="1" t="n">
+        <v>46239.48421683688</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>V3|VDA LA ASOMBROSA FIN EL MIRADOR ZONA R|AGUADAS</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>VDA LA ASOMBROSA FIN EL MIRADOR - ZONA R</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Aguadas</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>VEREDA LA ASOMBROSA FIN EL MIRADOR, Aguadas, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L287" t="n">
+        <v>2</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N287" s="1" t="n">
+        <v>46239.48424039681</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>V3|CLL 3 4 05 BARRIO SIN DEFINIR|AGUADAS</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>CLL 3 4 05 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Aguadas</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>CALLE 3 # 4-05, Aguadas, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>5.6143662</v>
+      </c>
+      <c r="G288" t="n">
+        <v>-75.4599833</v>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Aguadas</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L288" t="n">
+        <v>1</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Calle 3, Pore, Aguadas, Norte, Caldas, RAP Eje Cafetero, Colombia</t>
+        </is>
+      </c>
+      <c r="N288" s="1" t="n">
+        <v>46239.48425619714</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>V3|VDA SAN DIEGO PARTE BAJA ZONA RURAL|SALAMINA</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>VDA SAN DIEGO PARTE BAJA - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Salamina</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>VEREDA SAN DIEGO PARTE BAJA, Salamina, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L289" t="n">
+        <v>1</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N289" s="1" t="n">
+        <v>46239.48426620445</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>V3|VDA LA PALMA ZONA RURAL|SALAMINA</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>VDA LA PALMA - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Salamina</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>VEREDA LA PALMA, Salamina, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L290" t="n">
+        <v>1</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N290" s="1" t="n">
+        <v>46239.48427593186</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>V3|VDA LOS MANGOS FINCA LA ESTRELLA ZONA|SALAMINA</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>VDA LOS MANGOS FINCA LA ESTRELLA - ZONA</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Salamina</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>VEREDA LOS MANGOS FINCA LA ESTRELLA, Salamina, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L291" t="n">
+        <v>2</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N291" s="1" t="n">
+        <v>46239.48431161547</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>V3|VDA EL BOTON ZONA RURAL|SALAMINA</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>VDA EL BOTON - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Salamina</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>VEREDA EL BOTON, Salamina, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr"/>
+      <c r="J292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L292" t="n">
+        <v>1</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N292" s="1" t="n">
+        <v>46239.48431946863</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>V3|CRA 4 9 65 SAN FELIX ZONA RURAL|SALAMINA</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>CRA 4 9 65 - SAN FELIX - ZONA RURAL</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Salamina</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>CARRERA 4 # 9-65, SAN FELIX, Salamina, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>5.374608</v>
+      </c>
+      <c r="G293" t="n">
+        <v>-75.3733249</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Salamina</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>VALIDADA</t>
+        </is>
+      </c>
+      <c r="L293" t="n">
+        <v>1</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Carrera 4, San Félix, Salamina, Norte, Caldas, RAP del Agua y la Montaña, Colombia</t>
+        </is>
+      </c>
+      <c r="N293" s="1" t="n">
+        <v>46239.48433234775</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>V3|CRA 8 C 20 33 URB VILLAS DE SAN CARLOS|SANTA ROSA DE CABAL</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>CRA 8 C 20 33 URB VILLAS DE SAN CARLOS -</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Cabal</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>CARRERA 8C, Santa Rosa de Cabal, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr"/>
+      <c r="J294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L294" t="n">
+        <v>4</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N294" s="1" t="n">
+        <v>46239.48439731273</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>V3|MNZ 2 CAS 1 PIS 2 URB PORTAL DE LOS ANGE|BELEN DE UMBRIA</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>MNZ 2 CAS 1 PIS 2 URB PORTAL DE LOS ANGE</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Belen de Umbria</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>URBANIZACION PORTAL DE LOS ANGE, Belen de Umbria, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr"/>
+      <c r="J295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L295" t="n">
+        <v>2</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N295" s="1" t="n">
+        <v>46239.48447551134</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>V3|CLL 6 6 42 PIS 3 BARRIO SIN DEFINIR|MISTRATO</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>CLL 6 6 42 PIS 3 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Mistrato</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>CALLE 6, Mistrato, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L296" t="n">
+        <v>2</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N296" s="1" t="n">
+        <v>46239.48456710349</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>V3|VDA DOSQUEBRADAS VEREDA DOSQUEBRADAS|MISTRATO</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>VDA DOSQUEBRADAS - Vereda Dosquebradas</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Mistrato</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>VEREDA DOSQUEBRADAS, Mistrato, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr"/>
+      <c r="J297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L297" t="n">
+        <v>1</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N297" s="1" t="n">
+        <v>46239.48457655413</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>V3|VDA QUEBRADA ARRIBA VEREDA QUEBRADA AR|MISTRATO</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>VDA QUEBRADA ARRIBA - Vereda Quebrada Ar</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Mistrato</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>VEREDA QUEBRADA ARRIBA, Mistrato, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr"/>
+      <c r="J298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L298" t="n">
+        <v>1</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N298" s="1" t="n">
+        <v>46239.48459242565</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>V3|CLL 6 7 74 BARRIO SIN DEFINIR|MISTRATO</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>CLL 6 7 74 - BARRIO SIN DEFINIR</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Mistrato</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>URBANA</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>CALLE 6, Mistrato, Caldas, Colombia</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADA</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr"/>
+      <c r="J299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>SIN RESULTADOS</t>
+        </is>
+      </c>
+      <c r="L299" t="n">
+        <v>2</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>No se encontró una coordenada que coincidiera con el municipio esperado.</t>
+        </is>
+      </c>
+      <c r="N299" s="1" t="n">
+        <v>46239.48461040212</v>
       </c>
     </row>
   </sheetData>
